--- a/branches/feat/episodenart-auf-main/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/branches/feat/episodenart-auf-main/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:48:43+00:00</t>
+    <t>2026-09-30T19:56:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/episodenart-auf-main/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/branches/feat/episodenart-auf-main/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:56:57+00:00</t>
+    <t>2026-09-30T20:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/episodenart-auf-main/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/branches/feat/episodenart-auf-main/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:03:55+00:00</t>
+    <t>2026-10-01T05:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
